--- a/products.xlsx
+++ b/products.xlsx
@@ -1,26 +1,29 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\192.168.1.1\g\Meu site\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\192.168.1.1\g\Meu site\Mercado livre\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A24DB082-9B32-4D9E-92E6-346E9ABB0DFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3628DDF-9792-48E0-B9D4-07CEF4654D68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Produtos" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Produtos!$A$1:$D$1</definedName>
+  </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="341" uniqueCount="276">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="345" uniqueCount="279">
   <si>
     <t>name</t>
   </si>
@@ -848,6 +851,15 @@
   </si>
   <si>
     <t>https://meli.la/2ZZFc2P</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A PROMOÇÃO ARNO </t>
+  </si>
+  <si>
+    <t>https://th.bing.com/th/id/OIP.u_qxoOZ-lXFh-AonQbi-1gHaBy?w=346&amp;h=84&amp;c=7&amp;r=0&amp;o=7&amp;pid=1.7&amp;rm=3</t>
+  </si>
+  <si>
+    <t>https://lista.mercadolivre.com.br/loja/arno/</t>
   </si>
 </sst>
 </file>
@@ -957,7 +969,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -990,6 +1002,9 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hiperlink" xfId="1" builtinId="8"/>
@@ -1014,14 +1029,14 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>11</xdr:row>
+      <xdr:row>84</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>12</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
+      <xdr:row>85</xdr:row>
+      <xdr:rowOff>114299</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1062,14 +1077,14 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>11</xdr:row>
+      <xdr:row>84</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>12</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
+      <xdr:row>85</xdr:row>
+      <xdr:rowOff>114299</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1110,13 +1125,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>18</xdr:row>
+      <xdr:row>64</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>419100</xdr:colOff>
-      <xdr:row>20</xdr:row>
+      <xdr:row>66</xdr:row>
       <xdr:rowOff>49212</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -1206,14 +1221,14 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>46</xdr:row>
+      <xdr:row>17</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>419100</xdr:colOff>
-      <xdr:row>48</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>38101</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1254,13 +1269,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>72</xdr:row>
+      <xdr:row>18</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>419100</xdr:colOff>
-      <xdr:row>74</xdr:row>
+      <xdr:row>20</xdr:row>
       <xdr:rowOff>38100</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -1302,14 +1317,14 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>99</xdr:row>
+      <xdr:row>100</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>419100</xdr:colOff>
-      <xdr:row>101</xdr:row>
-      <xdr:rowOff>38099</xdr:rowOff>
+      <xdr:row>102</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1350,14 +1365,14 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>101</xdr:row>
+      <xdr:row>102</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>3905250</xdr:colOff>
-      <xdr:row>125</xdr:row>
-      <xdr:rowOff>189279</xdr:rowOff>
+      <xdr:row>126</xdr:row>
+      <xdr:rowOff>189278</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1398,13 +1413,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>126</xdr:row>
+      <xdr:row>127</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>419100</xdr:colOff>
-      <xdr:row>128</xdr:row>
+      <xdr:row>129</xdr:row>
       <xdr:rowOff>38100</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -1446,13 +1461,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>128</xdr:row>
+      <xdr:row>129</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>3905250</xdr:colOff>
-      <xdr:row>152</xdr:row>
+      <xdr:row>153</xdr:row>
       <xdr:rowOff>187022</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -1494,14 +1509,14 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>153</xdr:row>
+      <xdr:row>154</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>228600</xdr:colOff>
-      <xdr:row>154</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
+      <xdr:row>155</xdr:row>
+      <xdr:rowOff>38099</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1556,14 +1571,14 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>155</xdr:row>
+      <xdr:row>156</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>156</xdr:row>
-      <xdr:rowOff>114299</xdr:rowOff>
+      <xdr:row>157</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1605,13 +1620,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>18</xdr:row>
+      <xdr:row>64</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>419100</xdr:colOff>
-      <xdr:row>20</xdr:row>
+      <xdr:row>66</xdr:row>
       <xdr:rowOff>49212</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -1701,14 +1716,14 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>46</xdr:row>
+      <xdr:row>17</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>419100</xdr:colOff>
-      <xdr:row>48</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>38101</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1749,13 +1764,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>72</xdr:row>
+      <xdr:row>18</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>419100</xdr:colOff>
-      <xdr:row>74</xdr:row>
+      <xdr:row>20</xdr:row>
       <xdr:rowOff>38100</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -1797,14 +1812,14 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>99</xdr:row>
+      <xdr:row>100</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>419100</xdr:colOff>
-      <xdr:row>101</xdr:row>
-      <xdr:rowOff>38099</xdr:rowOff>
+      <xdr:row>102</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1845,14 +1860,14 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>101</xdr:row>
+      <xdr:row>102</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>3905250</xdr:colOff>
-      <xdr:row>125</xdr:row>
-      <xdr:rowOff>189279</xdr:rowOff>
+      <xdr:row>126</xdr:row>
+      <xdr:rowOff>189278</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1893,13 +1908,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>126</xdr:row>
+      <xdr:row>127</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>419100</xdr:colOff>
-      <xdr:row>128</xdr:row>
+      <xdr:row>129</xdr:row>
       <xdr:rowOff>38100</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -1941,13 +1956,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>128</xdr:row>
+      <xdr:row>129</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>3905250</xdr:colOff>
-      <xdr:row>152</xdr:row>
+      <xdr:row>153</xdr:row>
       <xdr:rowOff>187022</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -1989,14 +2004,14 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>153</xdr:row>
+      <xdr:row>154</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>228600</xdr:colOff>
-      <xdr:row>154</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
+      <xdr:row>155</xdr:row>
+      <xdr:rowOff>38099</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2051,14 +2066,14 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>155</xdr:row>
+      <xdr:row>156</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>156</xdr:row>
-      <xdr:rowOff>114299</xdr:rowOff>
+      <xdr:row>157</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -2100,13 +2115,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>19</xdr:row>
+      <xdr:row>3</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>20</xdr:row>
+      <xdr:row>4</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -2148,13 +2163,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>34</xdr:row>
+      <xdr:row>2</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>419100</xdr:colOff>
-      <xdr:row>36</xdr:row>
+      <xdr:row>4</xdr:row>
       <xdr:rowOff>38100</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -2196,14 +2211,14 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>36</xdr:row>
+      <xdr:row>58</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>3905250</xdr:colOff>
-      <xdr:row>61</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:row>83</xdr:row>
+      <xdr:rowOff>1</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -2292,13 +2307,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>63</xdr:row>
+      <xdr:row>36</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>3905250</xdr:colOff>
-      <xdr:row>87</xdr:row>
+      <xdr:row>60</xdr:row>
       <xdr:rowOff>171449</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -2340,14 +2355,14 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>88</xdr:row>
+      <xdr:row>89</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>419100</xdr:colOff>
-      <xdr:row>90</xdr:row>
-      <xdr:rowOff>9524</xdr:rowOff>
+      <xdr:row>91</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -2388,14 +2403,14 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>90</xdr:row>
+      <xdr:row>91</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>3905250</xdr:colOff>
-      <xdr:row>115</xdr:row>
-      <xdr:rowOff>1</xdr:rowOff>
+      <xdr:row>116</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -2436,13 +2451,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>115</xdr:row>
+      <xdr:row>116</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>419100</xdr:colOff>
-      <xdr:row>117</xdr:row>
+      <xdr:row>118</xdr:row>
       <xdr:rowOff>38100</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -2484,13 +2499,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>117</xdr:row>
+      <xdr:row>118</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>3905250</xdr:colOff>
-      <xdr:row>142</xdr:row>
+      <xdr:row>143</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -2532,13 +2547,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>142</xdr:row>
+      <xdr:row>143</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>419100</xdr:colOff>
-      <xdr:row>144</xdr:row>
+      <xdr:row>145</xdr:row>
       <xdr:rowOff>38100</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -2580,13 +2595,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>144</xdr:row>
+      <xdr:row>145</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>3905250</xdr:colOff>
-      <xdr:row>168</xdr:row>
+      <xdr:row>169</xdr:row>
       <xdr:rowOff>187022</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -2628,14 +2643,14 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>169</xdr:row>
+      <xdr:row>170</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>419100</xdr:colOff>
-      <xdr:row>171</xdr:row>
-      <xdr:rowOff>38101</xdr:rowOff>
+      <xdr:row>172</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -2676,14 +2691,14 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>171</xdr:row>
+      <xdr:row>172</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>3905250</xdr:colOff>
-      <xdr:row>195</xdr:row>
-      <xdr:rowOff>187022</xdr:rowOff>
+      <xdr:row>196</xdr:row>
+      <xdr:rowOff>187023</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -2724,13 +2739,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>196</xdr:row>
+      <xdr:row>197</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>228600</xdr:colOff>
-      <xdr:row>197</xdr:row>
+      <xdr:row>198</xdr:row>
       <xdr:rowOff>38100</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -2786,13 +2801,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>34</xdr:row>
+      <xdr:row>2</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>419100</xdr:colOff>
-      <xdr:row>36</xdr:row>
+      <xdr:row>4</xdr:row>
       <xdr:rowOff>38100</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -2834,14 +2849,14 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>36</xdr:row>
+      <xdr:row>58</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>3905250</xdr:colOff>
-      <xdr:row>61</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:row>83</xdr:row>
+      <xdr:rowOff>1</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -2930,13 +2945,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>63</xdr:row>
+      <xdr:row>36</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>3905250</xdr:colOff>
-      <xdr:row>87</xdr:row>
+      <xdr:row>60</xdr:row>
       <xdr:rowOff>171449</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -2978,14 +2993,14 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>88</xdr:row>
+      <xdr:row>89</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>419100</xdr:colOff>
-      <xdr:row>90</xdr:row>
-      <xdr:rowOff>9524</xdr:rowOff>
+      <xdr:row>91</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -3026,14 +3041,14 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>90</xdr:row>
+      <xdr:row>91</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>3905250</xdr:colOff>
-      <xdr:row>115</xdr:row>
-      <xdr:rowOff>1</xdr:rowOff>
+      <xdr:row>116</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -3074,13 +3089,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>115</xdr:row>
+      <xdr:row>116</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>419100</xdr:colOff>
-      <xdr:row>117</xdr:row>
+      <xdr:row>118</xdr:row>
       <xdr:rowOff>38100</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -3122,13 +3137,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>117</xdr:row>
+      <xdr:row>118</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>3905250</xdr:colOff>
-      <xdr:row>142</xdr:row>
+      <xdr:row>143</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -3170,13 +3185,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>142</xdr:row>
+      <xdr:row>143</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>419100</xdr:colOff>
-      <xdr:row>144</xdr:row>
+      <xdr:row>145</xdr:row>
       <xdr:rowOff>38100</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -3218,13 +3233,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>144</xdr:row>
+      <xdr:row>145</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>3905250</xdr:colOff>
-      <xdr:row>168</xdr:row>
+      <xdr:row>169</xdr:row>
       <xdr:rowOff>187022</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -3266,14 +3281,14 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>169</xdr:row>
+      <xdr:row>170</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>419100</xdr:colOff>
-      <xdr:row>171</xdr:row>
-      <xdr:rowOff>38101</xdr:rowOff>
+      <xdr:row>172</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -3314,14 +3329,14 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>171</xdr:row>
+      <xdr:row>172</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>3905250</xdr:colOff>
-      <xdr:row>195</xdr:row>
-      <xdr:rowOff>187022</xdr:rowOff>
+      <xdr:row>196</xdr:row>
+      <xdr:rowOff>187023</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -3362,13 +3377,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>196</xdr:row>
+      <xdr:row>197</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>228600</xdr:colOff>
-      <xdr:row>197</xdr:row>
+      <xdr:row>198</xdr:row>
       <xdr:rowOff>38100</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -3424,13 +3439,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>34</xdr:row>
+      <xdr:row>2</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>419100</xdr:colOff>
-      <xdr:row>36</xdr:row>
+      <xdr:row>4</xdr:row>
       <xdr:rowOff>38100</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -3472,14 +3487,14 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>36</xdr:row>
+      <xdr:row>58</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>3905250</xdr:colOff>
-      <xdr:row>61</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:row>83</xdr:row>
+      <xdr:rowOff>1</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -3568,13 +3583,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>63</xdr:row>
+      <xdr:row>36</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>3905250</xdr:colOff>
-      <xdr:row>87</xdr:row>
+      <xdr:row>60</xdr:row>
       <xdr:rowOff>171449</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -3616,14 +3631,14 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>88</xdr:row>
+      <xdr:row>89</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>419100</xdr:colOff>
-      <xdr:row>90</xdr:row>
-      <xdr:rowOff>9524</xdr:rowOff>
+      <xdr:row>91</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -3664,14 +3679,14 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>90</xdr:row>
+      <xdr:row>91</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>3905250</xdr:colOff>
-      <xdr:row>115</xdr:row>
-      <xdr:rowOff>1</xdr:rowOff>
+      <xdr:row>116</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -3712,13 +3727,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>115</xdr:row>
+      <xdr:row>116</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>419100</xdr:colOff>
-      <xdr:row>117</xdr:row>
+      <xdr:row>118</xdr:row>
       <xdr:rowOff>38100</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -3760,13 +3775,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>117</xdr:row>
+      <xdr:row>118</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>3905250</xdr:colOff>
-      <xdr:row>142</xdr:row>
+      <xdr:row>143</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -3808,13 +3823,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>142</xdr:row>
+      <xdr:row>143</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>419100</xdr:colOff>
-      <xdr:row>144</xdr:row>
+      <xdr:row>145</xdr:row>
       <xdr:rowOff>38100</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -3856,13 +3871,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>144</xdr:row>
+      <xdr:row>145</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>3905250</xdr:colOff>
-      <xdr:row>168</xdr:row>
+      <xdr:row>169</xdr:row>
       <xdr:rowOff>187022</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -3904,14 +3919,14 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>169</xdr:row>
+      <xdr:row>170</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>419100</xdr:colOff>
-      <xdr:row>171</xdr:row>
-      <xdr:rowOff>38101</xdr:rowOff>
+      <xdr:row>172</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -3952,14 +3967,14 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>171</xdr:row>
+      <xdr:row>172</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>3905250</xdr:colOff>
-      <xdr:row>195</xdr:row>
-      <xdr:rowOff>187022</xdr:rowOff>
+      <xdr:row>196</xdr:row>
+      <xdr:rowOff>187023</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -4000,13 +4015,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>196</xdr:row>
+      <xdr:row>197</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>228600</xdr:colOff>
-      <xdr:row>197</xdr:row>
+      <xdr:row>198</xdr:row>
       <xdr:rowOff>38100</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -4062,13 +4077,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>58</xdr:row>
+      <xdr:row>79</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>59</xdr:row>
+      <xdr:row>80</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -4110,13 +4125,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>60</xdr:row>
+      <xdr:row>57</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>61</xdr:row>
+      <xdr:row>58</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -4158,14 +4173,14 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>65</xdr:row>
+      <xdr:row>11</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>66</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>114301</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -4206,14 +4221,14 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>65</xdr:row>
+      <xdr:row>11</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>66</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>114301</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -4254,14 +4269,14 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>70</xdr:row>
+      <xdr:row>77</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>71</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
+      <xdr:row>78</xdr:row>
+      <xdr:rowOff>114301</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -4586,7 +4601,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D200"/>
+  <dimension ref="A1:D201"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="164" bestFit="1" customWidth="1"/>
@@ -4610,266 +4625,269 @@
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>12</v>
+      <c r="A2" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="B2" s="12" t="s">
+        <v>277</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>192</v>
+        <v>278</v>
       </c>
       <c r="D2" t="s">
-        <v>27</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>193</v>
+        <v>85</v>
+      </c>
+      <c r="B3" t="s">
+        <v>86</v>
+      </c>
+      <c r="C3" t="s">
+        <v>222</v>
       </c>
       <c r="D3" t="s">
-        <v>8</v>
+        <v>82</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>6</v>
+        <v>49</v>
       </c>
       <c r="B4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>194</v>
+        <v>50</v>
+      </c>
+      <c r="C4" t="s">
+        <v>209</v>
       </c>
       <c r="D4" t="s">
-        <v>8</v>
+        <v>22</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>9</v>
+        <v>187</v>
       </c>
       <c r="B5" t="s">
-        <v>10</v>
+        <v>188</v>
       </c>
       <c r="C5" t="s">
-        <v>195</v>
+        <v>267</v>
       </c>
       <c r="D5" t="s">
-        <v>8</v>
+        <v>42</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>13</v>
+        <v>169</v>
       </c>
       <c r="B6" t="s">
-        <v>14</v>
+        <v>170</v>
+      </c>
+      <c r="C6" t="s">
+        <v>258</v>
       </c>
       <c r="D6" t="s">
-        <v>64</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>15</v>
+        <v>57</v>
       </c>
       <c r="B7" t="s">
-        <v>16</v>
+        <v>56</v>
       </c>
       <c r="C7" t="s">
-        <v>196</v>
+        <v>211</v>
       </c>
       <c r="D7" t="s">
-        <v>17</v>
+        <v>58</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>18</v>
+        <v>118</v>
       </c>
       <c r="B8" t="s">
-        <v>23</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>197</v>
+        <v>237</v>
+      </c>
+      <c r="C8" t="s">
+        <v>236</v>
       </c>
       <c r="D8" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>20</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>21</v>
+        <v>183</v>
+      </c>
+      <c r="B9" t="s">
+        <v>184</v>
       </c>
       <c r="C9" t="s">
-        <v>198</v>
+        <v>265</v>
       </c>
       <c r="D9" t="s">
-        <v>22</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>37</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>36</v>
+        <v>139</v>
+      </c>
+      <c r="B10" t="s">
+        <v>140</v>
       </c>
       <c r="C10" t="s">
-        <v>199</v>
+        <v>245</v>
       </c>
       <c r="D10" t="s">
-        <v>24</v>
+        <v>123</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>116</v>
+        <v>70</v>
       </c>
       <c r="B11" t="s">
-        <v>117</v>
+        <v>71</v>
       </c>
       <c r="C11" t="s">
-        <v>200</v>
+        <v>216</v>
       </c>
       <c r="D11" t="s">
-        <v>24</v>
+        <v>55</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>25</v>
+        <v>153</v>
       </c>
       <c r="B12" t="s">
-        <v>26</v>
+        <v>152</v>
       </c>
       <c r="C12" t="s">
-        <v>201</v>
+        <v>250</v>
       </c>
       <c r="D12" t="s">
-        <v>27</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>28</v>
+        <v>76</v>
       </c>
       <c r="B13" t="s">
-        <v>29</v>
+        <v>77</v>
       </c>
       <c r="C13" t="s">
-        <v>202</v>
+        <v>219</v>
       </c>
       <c r="D13" t="s">
-        <v>19</v>
+        <v>42</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>30</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="C14" t="s">
-        <v>203</v>
+        <v>18</v>
+      </c>
+      <c r="B14" t="s">
+        <v>23</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>197</v>
       </c>
       <c r="D14" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="B15" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="C15" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="D15" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>39</v>
+        <v>175</v>
       </c>
       <c r="B16" t="s">
-        <v>38</v>
+        <v>176</v>
       </c>
       <c r="C16" t="s">
-        <v>205</v>
+        <v>261</v>
       </c>
       <c r="D16" t="s">
-        <v>24</v>
+        <v>55</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>40</v>
+        <v>119</v>
       </c>
       <c r="B17" t="s">
-        <v>41</v>
+        <v>120</v>
       </c>
       <c r="C17" t="s">
-        <v>206</v>
+        <v>238</v>
       </c>
       <c r="D17" t="s">
-        <v>42</v>
+        <v>82</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>43</v>
+        <v>110</v>
       </c>
       <c r="B18" t="s">
-        <v>44</v>
+        <v>111</v>
       </c>
       <c r="C18" t="s">
-        <v>207</v>
+        <v>274</v>
       </c>
       <c r="D18" t="s">
-        <v>45</v>
+        <v>32</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>46</v>
+        <v>166</v>
       </c>
       <c r="B19" t="s">
-        <v>47</v>
+        <v>167</v>
       </c>
       <c r="C19" t="s">
-        <v>208</v>
+        <v>257</v>
       </c>
       <c r="D19" t="s">
-        <v>48</v>
+        <v>168</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>49</v>
+        <v>185</v>
       </c>
       <c r="B20" t="s">
-        <v>50</v>
+        <v>186</v>
       </c>
       <c r="C20" t="s">
-        <v>209</v>
+        <v>266</v>
       </c>
       <c r="D20" t="s">
-        <v>22</v>
+        <v>42</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -4888,69 +4906,69 @@
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>53</v>
+        <v>74</v>
       </c>
       <c r="B22" t="s">
-        <v>54</v>
+        <v>75</v>
       </c>
       <c r="C22" t="s">
-        <v>272</v>
+        <v>218</v>
       </c>
       <c r="D22" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>57</v>
+        <v>160</v>
       </c>
       <c r="B23" t="s">
-        <v>56</v>
+        <v>161</v>
       </c>
       <c r="C23" t="s">
-        <v>211</v>
+        <v>254</v>
       </c>
       <c r="D23" t="s">
-        <v>58</v>
+        <v>123</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>59</v>
+        <v>6</v>
       </c>
       <c r="B24" t="s">
-        <v>60</v>
-      </c>
-      <c r="C24" t="s">
-        <v>212</v>
+        <v>7</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>194</v>
       </c>
       <c r="D24" t="s">
-        <v>58</v>
+        <v>8</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="B25" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C25" t="s">
-        <v>273</v>
+        <v>212</v>
       </c>
       <c r="D25" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>63</v>
+        <v>270</v>
       </c>
       <c r="B26" t="s">
-        <v>69</v>
+        <v>269</v>
       </c>
       <c r="C26" t="s">
-        <v>213</v>
+        <v>271</v>
       </c>
       <c r="D26" t="s">
         <v>42</v>
@@ -4958,170 +4976,167 @@
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>66</v>
+        <v>87</v>
       </c>
       <c r="B27" t="s">
-        <v>65</v>
+        <v>88</v>
       </c>
       <c r="C27" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
       <c r="D27" t="s">
-        <v>8</v>
+        <v>82</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>67</v>
+        <v>179</v>
       </c>
       <c r="B28" t="s">
-        <v>68</v>
+        <v>180</v>
       </c>
       <c r="C28" t="s">
-        <v>215</v>
+        <v>263</v>
       </c>
       <c r="D28" t="s">
-        <v>8</v>
+        <v>42</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>70</v>
+        <v>156</v>
       </c>
       <c r="B29" t="s">
-        <v>71</v>
+        <v>157</v>
       </c>
       <c r="C29" t="s">
-        <v>216</v>
+        <v>252</v>
       </c>
       <c r="D29" t="s">
-        <v>55</v>
+        <v>42</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>72</v>
+        <v>104</v>
       </c>
       <c r="B30" t="s">
-        <v>73</v>
-      </c>
-      <c r="C30" t="s">
-        <v>217</v>
+        <v>105</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>231</v>
       </c>
       <c r="D30" t="s">
-        <v>45</v>
+        <v>82</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>74</v>
+        <v>9</v>
       </c>
       <c r="B31" t="s">
-        <v>75</v>
+        <v>10</v>
       </c>
       <c r="C31" t="s">
-        <v>218</v>
+        <v>195</v>
       </c>
       <c r="D31" t="s">
-        <v>58</v>
+        <v>8</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>76</v>
+        <v>173</v>
       </c>
       <c r="B32" t="s">
-        <v>77</v>
+        <v>174</v>
       </c>
       <c r="C32" t="s">
-        <v>219</v>
+        <v>260</v>
       </c>
       <c r="D32" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>78</v>
+        <v>125</v>
       </c>
       <c r="B33" t="s">
-        <v>79</v>
+        <v>124</v>
       </c>
       <c r="C33" t="s">
-        <v>220</v>
+        <v>240</v>
       </c>
       <c r="D33" t="s">
-        <v>42</v>
+        <v>64</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>81</v>
+        <v>13</v>
       </c>
       <c r="B34" t="s">
-        <v>80</v>
-      </c>
-      <c r="C34" t="s">
-        <v>221</v>
+        <v>14</v>
       </c>
       <c r="D34" t="s">
-        <v>82</v>
+        <v>64</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>85</v>
+        <v>126</v>
       </c>
       <c r="B35" t="s">
-        <v>86</v>
+        <v>127</v>
       </c>
       <c r="C35" t="s">
-        <v>222</v>
+        <v>241</v>
       </c>
       <c r="D35" t="s">
-        <v>82</v>
+        <v>128</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>87</v>
+        <v>158</v>
       </c>
       <c r="B36" t="s">
-        <v>88</v>
+        <v>159</v>
       </c>
       <c r="C36" t="s">
-        <v>223</v>
+        <v>253</v>
       </c>
       <c r="D36" t="s">
-        <v>82</v>
+        <v>42</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A37" s="3" t="s">
-        <v>90</v>
+      <c r="A37" t="s">
+        <v>148</v>
       </c>
       <c r="B37" t="s">
-        <v>89</v>
+        <v>149</v>
       </c>
       <c r="C37" t="s">
-        <v>224</v>
+        <v>249</v>
       </c>
       <c r="D37" t="s">
-        <v>8</v>
+        <v>128</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A38" s="3" t="s">
-        <v>92</v>
+      <c r="A38" t="s">
+        <v>39</v>
       </c>
       <c r="B38" t="s">
-        <v>91</v>
+        <v>38</v>
       </c>
       <c r="C38" t="s">
-        <v>225</v>
+        <v>205</v>
       </c>
       <c r="D38" t="s">
-        <v>8</v>
+        <v>24</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
@@ -5140,276 +5155,279 @@
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>95</v>
-      </c>
-      <c r="B40" t="s">
-        <v>96</v>
+        <v>37</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>36</v>
       </c>
       <c r="C40" t="s">
-        <v>227</v>
+        <v>199</v>
       </c>
       <c r="D40" t="s">
-        <v>97</v>
+        <v>24</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>98</v>
+        <v>114</v>
       </c>
       <c r="B41" t="s">
-        <v>99</v>
+        <v>115</v>
       </c>
       <c r="C41" t="s">
-        <v>228</v>
+        <v>235</v>
       </c>
       <c r="D41" t="s">
-        <v>97</v>
+        <v>32</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>100</v>
+        <v>189</v>
       </c>
       <c r="B42" t="s">
-        <v>101</v>
+        <v>190</v>
       </c>
       <c r="C42" t="s">
-        <v>229</v>
+        <v>268</v>
       </c>
       <c r="D42" t="s">
-        <v>97</v>
+        <v>32</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="B43" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="C43" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="D43" t="s">
-        <v>42</v>
+        <v>97</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="B44" t="s">
-        <v>105</v>
-      </c>
-      <c r="C44" s="2" t="s">
-        <v>231</v>
+        <v>113</v>
+      </c>
+      <c r="C44" t="s">
+        <v>234</v>
       </c>
       <c r="D44" t="s">
-        <v>82</v>
+        <v>32</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>106</v>
+        <v>62</v>
       </c>
       <c r="B45" t="s">
-        <v>107</v>
+        <v>61</v>
       </c>
       <c r="C45" t="s">
-        <v>232</v>
+        <v>273</v>
       </c>
       <c r="D45" t="s">
-        <v>32</v>
+        <v>55</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>108</v>
+        <v>72</v>
       </c>
       <c r="B46" t="s">
-        <v>109</v>
-      </c>
-      <c r="C46" s="2" t="s">
-        <v>233</v>
+        <v>73</v>
+      </c>
+      <c r="C46" t="s">
+        <v>217</v>
       </c>
       <c r="D46" t="s">
-        <v>32</v>
+        <v>45</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>110</v>
+        <v>133</v>
       </c>
       <c r="B47" t="s">
-        <v>111</v>
+        <v>134</v>
       </c>
       <c r="C47" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="D47" t="s">
-        <v>32</v>
+        <v>58</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="B48" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="C48" t="s">
-        <v>234</v>
+        <v>200</v>
       </c>
       <c r="D48" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>114</v>
+        <v>98</v>
       </c>
       <c r="B49" t="s">
-        <v>115</v>
+        <v>99</v>
       </c>
       <c r="C49" t="s">
-        <v>235</v>
+        <v>228</v>
       </c>
       <c r="D49" t="s">
-        <v>32</v>
+        <v>97</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>118</v>
+        <v>53</v>
       </c>
       <c r="B50" t="s">
-        <v>237</v>
+        <v>54</v>
       </c>
       <c r="C50" t="s">
-        <v>236</v>
+        <v>272</v>
       </c>
       <c r="D50" t="s">
-        <v>32</v>
+        <v>55</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>119</v>
-      </c>
-      <c r="B51" t="s">
-        <v>120</v>
-      </c>
-      <c r="C51" t="s">
-        <v>238</v>
+        <v>5</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>193</v>
       </c>
       <c r="D51" t="s">
-        <v>82</v>
+        <v>8</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A52" t="s">
-        <v>121</v>
+      <c r="A52" s="3" t="s">
+        <v>92</v>
       </c>
       <c r="B52" t="s">
-        <v>122</v>
+        <v>91</v>
       </c>
       <c r="C52" t="s">
-        <v>239</v>
+        <v>225</v>
       </c>
       <c r="D52" t="s">
-        <v>123</v>
+        <v>8</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>125</v>
+        <v>181</v>
       </c>
       <c r="B53" t="s">
-        <v>124</v>
+        <v>182</v>
       </c>
       <c r="C53" t="s">
-        <v>240</v>
+        <v>264</v>
       </c>
       <c r="D53" t="s">
-        <v>64</v>
+        <v>42</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>126</v>
+        <v>43</v>
       </c>
       <c r="B54" t="s">
-        <v>127</v>
+        <v>44</v>
       </c>
       <c r="C54" t="s">
-        <v>241</v>
+        <v>207</v>
       </c>
       <c r="D54" t="s">
-        <v>128</v>
+        <v>45</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>130</v>
-      </c>
-      <c r="B55" t="s">
-        <v>129</v>
+        <v>30</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>31</v>
       </c>
       <c r="C55" t="s">
-        <v>242</v>
+        <v>203</v>
       </c>
       <c r="D55" t="s">
-        <v>123</v>
+        <v>32</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>131</v>
+        <v>155</v>
       </c>
       <c r="B56" t="s">
-        <v>132</v>
+        <v>154</v>
       </c>
       <c r="C56" t="s">
-        <v>243</v>
+        <v>251</v>
       </c>
       <c r="D56" t="s">
-        <v>58</v>
+        <v>8</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>133</v>
+        <v>151</v>
       </c>
       <c r="B57" t="s">
-        <v>134</v>
+        <v>150</v>
       </c>
       <c r="C57" t="s">
-        <v>275</v>
+        <v>191</v>
       </c>
       <c r="D57" t="s">
-        <v>58</v>
+        <v>42</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="B58" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="C58" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="D58" t="s">
-        <v>55</v>
+        <v>143</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A59" t="s">
-        <v>138</v>
+      <c r="A59" s="3" t="s">
+        <v>90</v>
       </c>
       <c r="B59" t="s">
-        <v>137</v>
+        <v>89</v>
+      </c>
+      <c r="C59" t="s">
+        <v>224</v>
       </c>
       <c r="D59" t="s">
         <v>8</v>
@@ -5417,30 +5435,30 @@
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="B60" t="s">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="C60" t="s">
-        <v>245</v>
+        <v>229</v>
       </c>
       <c r="D60" t="s">
-        <v>123</v>
+        <v>97</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>141</v>
+        <v>15</v>
       </c>
       <c r="B61" t="s">
-        <v>142</v>
+        <v>16</v>
       </c>
       <c r="C61" t="s">
-        <v>246</v>
+        <v>196</v>
       </c>
       <c r="D61" t="s">
-        <v>143</v>
+        <v>17</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.25">
@@ -5473,69 +5491,69 @@
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>148</v>
+        <v>63</v>
       </c>
       <c r="B64" t="s">
-        <v>149</v>
+        <v>69</v>
       </c>
       <c r="C64" t="s">
-        <v>249</v>
+        <v>213</v>
       </c>
       <c r="D64" t="s">
-        <v>128</v>
+        <v>42</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>151</v>
+        <v>46</v>
       </c>
       <c r="B65" t="s">
-        <v>150</v>
+        <v>47</v>
       </c>
       <c r="C65" t="s">
-        <v>191</v>
+        <v>208</v>
       </c>
       <c r="D65" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>153</v>
+        <v>131</v>
       </c>
       <c r="B66" t="s">
-        <v>152</v>
+        <v>132</v>
       </c>
       <c r="C66" t="s">
-        <v>250</v>
+        <v>243</v>
       </c>
       <c r="D66" t="s">
-        <v>8</v>
+        <v>58</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>155</v>
+        <v>33</v>
       </c>
       <c r="B67" t="s">
-        <v>154</v>
+        <v>34</v>
       </c>
       <c r="C67" t="s">
-        <v>251</v>
+        <v>204</v>
       </c>
       <c r="D67" t="s">
-        <v>8</v>
+        <v>35</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>156</v>
+        <v>171</v>
       </c>
       <c r="B68" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="C68" t="s">
-        <v>252</v>
+        <v>259</v>
       </c>
       <c r="D68" t="s">
         <v>42</v>
@@ -5543,97 +5561,97 @@
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>158</v>
+        <v>67</v>
       </c>
       <c r="B69" t="s">
-        <v>159</v>
+        <v>68</v>
       </c>
       <c r="C69" t="s">
-        <v>253</v>
+        <v>215</v>
       </c>
       <c r="D69" t="s">
-        <v>42</v>
+        <v>8</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>160</v>
+        <v>66</v>
       </c>
       <c r="B70" t="s">
-        <v>161</v>
+        <v>65</v>
       </c>
       <c r="C70" t="s">
-        <v>254</v>
+        <v>214</v>
       </c>
       <c r="D70" t="s">
-        <v>123</v>
+        <v>8</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>162</v>
+        <v>135</v>
       </c>
       <c r="B71" t="s">
-        <v>163</v>
+        <v>136</v>
       </c>
       <c r="C71" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
       <c r="D71" t="s">
-        <v>123</v>
+        <v>55</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>164</v>
+        <v>106</v>
       </c>
       <c r="B72" t="s">
-        <v>165</v>
+        <v>107</v>
       </c>
       <c r="C72" t="s">
-        <v>256</v>
+        <v>232</v>
       </c>
       <c r="D72" t="s">
-        <v>128</v>
+        <v>32</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>166</v>
+        <v>108</v>
       </c>
       <c r="B73" t="s">
-        <v>167</v>
-      </c>
-      <c r="C73" t="s">
-        <v>257</v>
+        <v>109</v>
+      </c>
+      <c r="C73" s="2" t="s">
+        <v>233</v>
       </c>
       <c r="D73" t="s">
-        <v>168</v>
+        <v>32</v>
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>169</v>
+        <v>78</v>
       </c>
       <c r="B74" t="s">
-        <v>170</v>
+        <v>79</v>
       </c>
       <c r="C74" t="s">
-        <v>258</v>
+        <v>220</v>
       </c>
       <c r="D74" t="s">
-        <v>8</v>
+        <v>42</v>
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>171</v>
+        <v>102</v>
       </c>
       <c r="B75" t="s">
-        <v>172</v>
+        <v>103</v>
       </c>
       <c r="C75" t="s">
-        <v>259</v>
+        <v>230</v>
       </c>
       <c r="D75" t="s">
         <v>42</v>
@@ -5641,97 +5659,94 @@
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>173</v>
+        <v>130</v>
       </c>
       <c r="B76" t="s">
-        <v>174</v>
+        <v>129</v>
       </c>
       <c r="C76" t="s">
-        <v>260</v>
+        <v>242</v>
       </c>
       <c r="D76" t="s">
-        <v>55</v>
+        <v>123</v>
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>175</v>
+        <v>121</v>
       </c>
       <c r="B77" t="s">
-        <v>176</v>
+        <v>122</v>
       </c>
       <c r="C77" t="s">
-        <v>261</v>
+        <v>239</v>
       </c>
       <c r="D77" t="s">
-        <v>55</v>
+        <v>123</v>
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>177</v>
+        <v>162</v>
       </c>
       <c r="B78" t="s">
-        <v>178</v>
+        <v>163</v>
       </c>
       <c r="C78" t="s">
-        <v>262</v>
+        <v>255</v>
       </c>
       <c r="D78" t="s">
-        <v>42</v>
+        <v>123</v>
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>179</v>
+        <v>81</v>
       </c>
       <c r="B79" t="s">
-        <v>180</v>
+        <v>80</v>
       </c>
       <c r="C79" t="s">
-        <v>263</v>
+        <v>221</v>
       </c>
       <c r="D79" t="s">
-        <v>42</v>
+        <v>82</v>
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>181</v>
+        <v>138</v>
       </c>
       <c r="B80" t="s">
-        <v>182</v>
-      </c>
-      <c r="C80" t="s">
-        <v>264</v>
+        <v>137</v>
       </c>
       <c r="D80" t="s">
-        <v>42</v>
+        <v>8</v>
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>183</v>
+        <v>164</v>
       </c>
       <c r="B81" t="s">
-        <v>184</v>
+        <v>165</v>
       </c>
       <c r="C81" t="s">
-        <v>265</v>
+        <v>256</v>
       </c>
       <c r="D81" t="s">
-        <v>8</v>
+        <v>128</v>
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>185</v>
+        <v>40</v>
       </c>
       <c r="B82" t="s">
-        <v>186</v>
+        <v>41</v>
       </c>
       <c r="C82" t="s">
-        <v>266</v>
+        <v>206</v>
       </c>
       <c r="D82" t="s">
         <v>42</v>
@@ -5739,13 +5754,13 @@
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>187</v>
+        <v>177</v>
       </c>
       <c r="B83" t="s">
-        <v>188</v>
+        <v>178</v>
       </c>
       <c r="C83" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="D83" t="s">
         <v>42</v>
@@ -5753,44 +5768,55 @@
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>189</v>
-      </c>
-      <c r="B84" t="s">
-        <v>190</v>
-      </c>
-      <c r="C84" t="s">
-        <v>268</v>
+        <v>11</v>
+      </c>
+      <c r="B84" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C84" s="2" t="s">
+        <v>192</v>
       </c>
       <c r="D84" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>270</v>
+        <v>25</v>
       </c>
       <c r="B85" t="s">
-        <v>269</v>
+        <v>26</v>
       </c>
       <c r="C85" t="s">
-        <v>271</v>
+        <v>201</v>
       </c>
       <c r="D85" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="88" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="89" spans="1:4" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A89" s="10"/>
-    </row>
-    <row r="90" spans="1:4" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A90" s="4"/>
-    </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A91" s="5"/>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>20</v>
+      </c>
+      <c r="B86" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C86" t="s">
+        <v>198</v>
+      </c>
+      <c r="D86" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="90" spans="1:4" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A90" s="10"/>
+    </row>
+    <row r="91" spans="1:4" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A91" s="4"/>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A92" s="4"/>
+      <c r="A92" s="5"/>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A93" s="4"/>
@@ -5859,19 +5885,19 @@
       <c r="A114" s="4"/>
     </row>
     <row r="115" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A115" s="6"/>
+      <c r="A115" s="4"/>
     </row>
     <row r="116" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A116" s="6"/>
     </row>
     <row r="117" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A117" s="4"/>
+      <c r="A117" s="6"/>
     </row>
     <row r="118" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A118" s="5"/>
+      <c r="A118" s="4"/>
     </row>
     <row r="119" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A119" s="4"/>
+      <c r="A119" s="5"/>
     </row>
     <row r="120" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A120" s="4"/>
@@ -5940,19 +5966,19 @@
       <c r="A141" s="4"/>
     </row>
     <row r="142" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A142" s="6"/>
+      <c r="A142" s="4"/>
     </row>
     <row r="143" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A143" s="6"/>
     </row>
     <row r="144" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A144" s="4"/>
+      <c r="A144" s="6"/>
     </row>
     <row r="145" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A145" s="5"/>
+      <c r="A145" s="4"/>
     </row>
     <row r="146" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A146" s="4"/>
+      <c r="A146" s="5"/>
     </row>
     <row r="147" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A147" s="4"/>
@@ -6021,19 +6047,19 @@
       <c r="A168" s="4"/>
     </row>
     <row r="169" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A169" s="6"/>
+      <c r="A169" s="4"/>
     </row>
     <row r="170" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A170" s="6"/>
     </row>
     <row r="171" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A171" s="4"/>
+      <c r="A171" s="6"/>
     </row>
     <row r="172" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A172" s="5"/>
+      <c r="A172" s="4"/>
     </row>
     <row r="173" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A173" s="4"/>
+      <c r="A173" s="5"/>
     </row>
     <row r="174" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A174" s="4"/>
@@ -6102,39 +6128,50 @@
       <c r="A195" s="4"/>
     </row>
     <row r="196" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A196" s="7"/>
+      <c r="A196" s="4"/>
     </row>
     <row r="197" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A197" s="7"/>
     </row>
     <row r="198" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A198" s="8" t="s">
+      <c r="A198" s="7"/>
+    </row>
+    <row r="199" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A199" s="8" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="199" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A199" s="9" t="s">
+    <row r="200" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A200" s="9" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="200" spans="1:1" ht="21.75" x14ac:dyDescent="0.25">
-      <c r="A200" s="11" t="s">
+    <row r="201" spans="1:1" ht="21.75" x14ac:dyDescent="0.25">
+      <c r="A201" s="11" t="s">
         <v>85</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:D1" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D85">
+      <sortCondition ref="A1"/>
+    </sortState>
+  </autoFilter>
   <hyperlinks>
-    <hyperlink ref="B3" r:id="rId1" xr:uid="{DCE316A2-6F5F-4239-8670-A2501AD068BA}"/>
-    <hyperlink ref="B2" r:id="rId2" xr:uid="{E75C36C1-9EBF-4C4A-9D5E-6178C36287DA}"/>
-    <hyperlink ref="B9" r:id="rId3" xr:uid="{E7AF4AD0-FB67-4D18-A345-7AC735B2DDD9}"/>
-    <hyperlink ref="B10" r:id="rId4" xr:uid="{5ED3D7ED-FC6D-4C44-8B5F-671739F6A728}"/>
-    <hyperlink ref="B14" r:id="rId5" xr:uid="{AED35A75-AE1C-4AD0-9122-E943C0451F4B}"/>
-    <hyperlink ref="A198" r:id="rId6" location="redirect=landing_international&amp;origin=vip" display="https://www.mercadolivre.com.br/importados/compra-internacional - redirect=landing_international&amp;origin=vip" xr:uid="{CC0DCAE0-A290-49ED-AC96-9E0C27938302}"/>
-    <hyperlink ref="B77" r:id="rId7" xr:uid="{C44C884A-2B1F-46D5-849E-2AEEA7727C26}"/>
-    <hyperlink ref="C46" r:id="rId8" xr:uid="{D7CE1F55-B7E3-4E3A-87FB-E2DE297FF331}"/>
+    <hyperlink ref="B51" r:id="rId1" xr:uid="{DCE316A2-6F5F-4239-8670-A2501AD068BA}"/>
+    <hyperlink ref="B84" r:id="rId2" xr:uid="{E75C36C1-9EBF-4C4A-9D5E-6178C36287DA}"/>
+    <hyperlink ref="B86" r:id="rId3" xr:uid="{E7AF4AD0-FB67-4D18-A345-7AC735B2DDD9}"/>
+    <hyperlink ref="B40" r:id="rId4" xr:uid="{5ED3D7ED-FC6D-4C44-8B5F-671739F6A728}"/>
+    <hyperlink ref="B55" r:id="rId5" xr:uid="{AED35A75-AE1C-4AD0-9122-E943C0451F4B}"/>
+    <hyperlink ref="A199" r:id="rId6" location="redirect=landing_international&amp;origin=vip" display="https://www.mercadolivre.com.br/importados/compra-internacional - redirect=landing_international&amp;origin=vip" xr:uid="{CC0DCAE0-A290-49ED-AC96-9E0C27938302}"/>
+    <hyperlink ref="B16" r:id="rId7" xr:uid="{C44C884A-2B1F-46D5-849E-2AEEA7727C26}"/>
+    <hyperlink ref="C73" r:id="rId8" xr:uid="{D7CE1F55-B7E3-4E3A-87FB-E2DE297FF331}"/>
+    <hyperlink ref="C84" r:id="rId9" xr:uid="{7F6784A7-D9C7-49C7-ADDF-58FC99A98E87}"/>
+    <hyperlink ref="A2" r:id="rId10" display="https://lista.mercadolivre.com.br/loja/arno/" xr:uid="{C2FE83C8-65E9-44C2-AED5-3D82B99C1460}"/>
+    <hyperlink ref="C2" r:id="rId11" xr:uid="{A62E20C5-F356-49A0-8D26-E46AD707FE03}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId9"/>
-  <drawing r:id="rId10"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId12"/>
+  <drawing r:id="rId13"/>
 </worksheet>
 </file>
--- a/products.xlsx
+++ b/products.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\192.168.1.1\g\Meu site\Mercado livre\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3628DDF-9792-48E0-B9D4-07CEF4654D68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D10E2730-31F3-4DB8-8BA0-158E021BFB2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -853,13 +853,13 @@
     <t>https://meli.la/2ZZFc2P</t>
   </si>
   <si>
-    <t xml:space="preserve">A PROMOÇÃO ARNO </t>
-  </si>
-  <si>
     <t>https://th.bing.com/th/id/OIP.u_qxoOZ-lXFh-AonQbi-1gHaBy?w=346&amp;h=84&amp;c=7&amp;r=0&amp;o=7&amp;pid=1.7&amp;rm=3</t>
   </si>
   <si>
     <t>https://lista.mercadolivre.com.br/loja/arno/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10%  PROMOÇÃO ARNO </t>
   </si>
 </sst>
 </file>
@@ -4626,13 +4626,13 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="B2" s="12" t="s">
         <v>276</v>
       </c>
-      <c r="B2" s="12" t="s">
+      <c r="C2" s="2" t="s">
         <v>277</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>278</v>
       </c>
       <c r="D2" t="s">
         <v>8</v>

--- a/products.xlsx
+++ b/products.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\192.168.1.1\g\Meu site\Mercado livre\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D10E2730-31F3-4DB8-8BA0-158E021BFB2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73912306-EA5F-45A4-BA0F-E3E1F4192F37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -853,13 +853,13 @@
     <t>https://meli.la/2ZZFc2P</t>
   </si>
   <si>
-    <t>https://th.bing.com/th/id/OIP.u_qxoOZ-lXFh-AonQbi-1gHaBy?w=346&amp;h=84&amp;c=7&amp;r=0&amp;o=7&amp;pid=1.7&amp;rm=3</t>
-  </si>
-  <si>
     <t>https://lista.mercadolivre.com.br/loja/arno/</t>
   </si>
   <si>
-    <t xml:space="preserve">10%  PROMOÇÃO ARNO </t>
+    <t>10%  PROMOÇÃO ARNO USO O CUPOM: #OFFNAINFI10INFNITY</t>
+  </si>
+  <si>
+    <t>https://th.bing.com/th/id/OIP.Hld4w1H8cK960WzYCDa-qAAAAA?w=288&amp;h=104&amp;c=7&amp;r=0&amp;o=7&amp;pid=1.7&amp;rm=3</t>
   </si>
 </sst>
 </file>
@@ -4626,13 +4626,13 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="B2" s="12" t="s">
         <v>278</v>
       </c>
-      <c r="B2" s="12" t="s">
+      <c r="C2" s="2" t="s">
         <v>276</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>277</v>
       </c>
       <c r="D2" t="s">
         <v>8</v>

--- a/products.xlsx
+++ b/products.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\192.168.1.1\g\Meu site\Mercado livre\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73912306-EA5F-45A4-BA0F-E3E1F4192F37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{937DFAD3-7FD2-499A-B74E-CA0FCDA5F015}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -856,10 +856,10 @@
     <t>https://lista.mercadolivre.com.br/loja/arno/</t>
   </si>
   <si>
-    <t>10%  PROMOÇÃO ARNO USO O CUPOM: #OFFNAINFI10INFNITY</t>
-  </si>
-  <si>
     <t>https://th.bing.com/th/id/OIP.Hld4w1H8cK960WzYCDa-qAAAAA?w=288&amp;h=104&amp;c=7&amp;r=0&amp;o=7&amp;pid=1.7&amp;rm=3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10%  PROMOÇÃO ARNO VÁLIDO ATÉ 21/04/26 USE O CUPOM: #INFINITY10OFF   </t>
   </si>
 </sst>
 </file>
@@ -4626,10 +4626,10 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="B2" s="12" t="s">
         <v>277</v>
-      </c>
-      <c r="B2" s="12" t="s">
-        <v>278</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>276</v>

--- a/products.xlsx
+++ b/products.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\192.168.1.1\g\Meu site\Mercado livre\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{937DFAD3-7FD2-499A-B74E-CA0FCDA5F015}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75E48627-3EB9-4A64-BF70-C75A9F3125B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Produtos" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="345" uniqueCount="279">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="337" uniqueCount="274">
   <si>
     <t>name</t>
   </si>
@@ -283,9 +283,6 @@
     <t>50 Unidades De Copos De Rede De Plástico, Malha Com Fenda</t>
   </si>
   <si>
-    <t>https://http2.mlstatic.com/D_NQ_NP_2X_738534-MLB99276147747_112025-F.webp</t>
-  </si>
-  <si>
     <t>Espanta Mosca Ventilador Repelente De Mosquito Para Mesa</t>
   </si>
   <si>
@@ -691,9 +688,6 @@
     <t>https://meli.la/1QmhH6z</t>
   </si>
   <si>
-    <t>https://meli.la/1jpBfhb</t>
-  </si>
-  <si>
     <t>https://meli.la/1BQmqfU</t>
   </si>
   <si>
@@ -851,15 +845,6 @@
   </si>
   <si>
     <t>https://meli.la/2ZZFc2P</t>
-  </si>
-  <si>
-    <t>https://lista.mercadolivre.com.br/loja/arno/</t>
-  </si>
-  <si>
-    <t>https://th.bing.com/th/id/OIP.Hld4w1H8cK960WzYCDa-qAAAAA?w=288&amp;h=104&amp;c=7&amp;r=0&amp;o=7&amp;pid=1.7&amp;rm=3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10%  PROMOÇÃO ARNO VÁLIDO ATÉ 21/04/26 USE O CUPOM: #INFINITY10OFF   </t>
   </si>
 </sst>
 </file>
@@ -969,7 +954,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -1002,9 +987,6 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hiperlink" xfId="1" builtinId="8"/>
@@ -1029,14 +1011,14 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>84</xdr:row>
+      <xdr:row>82</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>85</xdr:row>
-      <xdr:rowOff>114299</xdr:rowOff>
+      <xdr:row>83</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1077,14 +1059,14 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>84</xdr:row>
+      <xdr:row>82</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>85</xdr:row>
-      <xdr:rowOff>114299</xdr:rowOff>
+      <xdr:row>83</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1125,14 +1107,14 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
+      <xdr:row>62</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>419100</xdr:colOff>
       <xdr:row>64</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>419100</xdr:colOff>
-      <xdr:row>66</xdr:row>
-      <xdr:rowOff>49212</xdr:rowOff>
+      <xdr:rowOff>49211</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1173,13 +1155,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>20</xdr:row>
+      <xdr:row>18</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>3905250</xdr:colOff>
-      <xdr:row>45</xdr:row>
+      <xdr:row>43</xdr:row>
       <xdr:rowOff>1</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -1221,14 +1203,14 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>419100</xdr:colOff>
       <xdr:row>17</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>419100</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>38101</xdr:rowOff>
+      <xdr:rowOff>38100</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1269,13 +1251,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>419100</xdr:colOff>
       <xdr:row>18</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>419100</xdr:colOff>
-      <xdr:row>20</xdr:row>
       <xdr:rowOff>38100</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -1317,13 +1299,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
+      <xdr:row>98</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>419100</xdr:colOff>
       <xdr:row>100</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>419100</xdr:colOff>
-      <xdr:row>102</xdr:row>
       <xdr:rowOff>38100</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -1365,13 +1347,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>102</xdr:row>
+      <xdr:row>100</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>3905250</xdr:colOff>
-      <xdr:row>126</xdr:row>
+      <xdr:row>124</xdr:row>
       <xdr:rowOff>189278</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -1413,14 +1395,14 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
+      <xdr:row>125</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>419100</xdr:colOff>
       <xdr:row>127</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>419100</xdr:colOff>
-      <xdr:row>129</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
+      <xdr:rowOff>38099</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1461,13 +1443,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>129</xdr:row>
+      <xdr:row>127</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>3905250</xdr:colOff>
-      <xdr:row>153</xdr:row>
+      <xdr:row>151</xdr:row>
       <xdr:rowOff>187022</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -1509,13 +1491,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>154</xdr:row>
+      <xdr:row>152</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>228600</xdr:colOff>
-      <xdr:row>155</xdr:row>
+      <xdr:row>153</xdr:row>
       <xdr:rowOff>38099</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1571,14 +1553,14 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>156</xdr:row>
+      <xdr:row>154</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>157</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
+      <xdr:row>155</xdr:row>
+      <xdr:rowOff>114299</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1620,14 +1602,14 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
+      <xdr:row>62</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>419100</xdr:colOff>
       <xdr:row>64</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>419100</xdr:colOff>
-      <xdr:row>66</xdr:row>
-      <xdr:rowOff>49212</xdr:rowOff>
+      <xdr:rowOff>49211</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1668,13 +1650,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>20</xdr:row>
+      <xdr:row>18</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>3905250</xdr:colOff>
-      <xdr:row>45</xdr:row>
+      <xdr:row>43</xdr:row>
       <xdr:rowOff>1</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -1716,14 +1698,14 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>419100</xdr:colOff>
       <xdr:row>17</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>419100</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>38101</xdr:rowOff>
+      <xdr:rowOff>38100</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1764,13 +1746,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>419100</xdr:colOff>
       <xdr:row>18</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>419100</xdr:colOff>
-      <xdr:row>20</xdr:row>
       <xdr:rowOff>38100</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -1812,13 +1794,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
+      <xdr:row>98</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>419100</xdr:colOff>
       <xdr:row>100</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>419100</xdr:colOff>
-      <xdr:row>102</xdr:row>
       <xdr:rowOff>38100</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -1860,13 +1842,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>102</xdr:row>
+      <xdr:row>100</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>3905250</xdr:colOff>
-      <xdr:row>126</xdr:row>
+      <xdr:row>124</xdr:row>
       <xdr:rowOff>189278</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -1908,14 +1890,14 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
+      <xdr:row>125</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>419100</xdr:colOff>
       <xdr:row>127</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>419100</xdr:colOff>
-      <xdr:row>129</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
+      <xdr:rowOff>38099</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1956,13 +1938,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>129</xdr:row>
+      <xdr:row>127</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>3905250</xdr:colOff>
-      <xdr:row>153</xdr:row>
+      <xdr:row>151</xdr:row>
       <xdr:rowOff>187022</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -2004,13 +1986,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>154</xdr:row>
+      <xdr:row>152</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>228600</xdr:colOff>
-      <xdr:row>155</xdr:row>
+      <xdr:row>153</xdr:row>
       <xdr:rowOff>38099</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -2066,14 +2048,14 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>156</xdr:row>
+      <xdr:row>154</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>157</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
+      <xdr:row>155</xdr:row>
+      <xdr:rowOff>114299</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -2115,13 +2097,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>3</xdr:row>
+      <xdr:row>1</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>4</xdr:row>
+      <xdr:row>2</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -2163,13 +2145,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>2</xdr:row>
+      <xdr:row>1</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>419100</xdr:colOff>
-      <xdr:row>4</xdr:row>
+      <xdr:row>3</xdr:row>
       <xdr:rowOff>38100</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -2211,13 +2193,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>58</xdr:row>
+      <xdr:row>56</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>3905250</xdr:colOff>
-      <xdr:row>83</xdr:row>
+      <xdr:row>81</xdr:row>
       <xdr:rowOff>1</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -2259,13 +2241,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
+      <xdr:row>59</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>419100</xdr:colOff>
       <xdr:row>61</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>419100</xdr:colOff>
-      <xdr:row>63</xdr:row>
       <xdr:rowOff>38101</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -2307,13 +2289,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>36</xdr:row>
+      <xdr:row>34</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>3905250</xdr:colOff>
-      <xdr:row>60</xdr:row>
+      <xdr:row>58</xdr:row>
       <xdr:rowOff>171449</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -2355,13 +2337,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
+      <xdr:row>87</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>419100</xdr:colOff>
       <xdr:row>89</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>419100</xdr:colOff>
-      <xdr:row>91</xdr:row>
       <xdr:rowOff>9525</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -2403,13 +2385,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>91</xdr:row>
+      <xdr:row>89</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>3905250</xdr:colOff>
-      <xdr:row>116</xdr:row>
+      <xdr:row>114</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -2451,13 +2433,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
+      <xdr:row>114</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>419100</xdr:colOff>
       <xdr:row>116</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>419100</xdr:colOff>
-      <xdr:row>118</xdr:row>
       <xdr:rowOff>38100</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -2499,14 +2481,14 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>118</xdr:row>
+      <xdr:row>116</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>3905250</xdr:colOff>
-      <xdr:row>143</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:row>141</xdr:row>
+      <xdr:rowOff>1</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -2547,14 +2529,14 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
+      <xdr:row>141</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>419100</xdr:colOff>
       <xdr:row>143</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>419100</xdr:colOff>
-      <xdr:row>145</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
+      <xdr:rowOff>38099</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -2595,14 +2577,14 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>145</xdr:row>
+      <xdr:row>143</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>3905250</xdr:colOff>
-      <xdr:row>169</xdr:row>
-      <xdr:rowOff>187022</xdr:rowOff>
+      <xdr:row>167</xdr:row>
+      <xdr:rowOff>187023</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -2643,14 +2625,14 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
+      <xdr:row>168</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>419100</xdr:colOff>
       <xdr:row>170</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>419100</xdr:colOff>
-      <xdr:row>172</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
+      <xdr:rowOff>38101</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -2691,14 +2673,14 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>172</xdr:row>
+      <xdr:row>170</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>3905250</xdr:colOff>
-      <xdr:row>196</xdr:row>
-      <xdr:rowOff>187023</xdr:rowOff>
+      <xdr:row>194</xdr:row>
+      <xdr:rowOff>187022</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -2739,14 +2721,14 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>197</xdr:row>
+      <xdr:row>195</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>228600</xdr:colOff>
-      <xdr:row>198</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
+      <xdr:row>196</xdr:row>
+      <xdr:rowOff>38101</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2801,13 +2783,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>2</xdr:row>
+      <xdr:row>1</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>419100</xdr:colOff>
-      <xdr:row>4</xdr:row>
+      <xdr:row>3</xdr:row>
       <xdr:rowOff>38100</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -2849,13 +2831,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>58</xdr:row>
+      <xdr:row>56</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>3905250</xdr:colOff>
-      <xdr:row>83</xdr:row>
+      <xdr:row>81</xdr:row>
       <xdr:rowOff>1</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -2897,13 +2879,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
+      <xdr:row>59</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>419100</xdr:colOff>
       <xdr:row>61</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>419100</xdr:colOff>
-      <xdr:row>63</xdr:row>
       <xdr:rowOff>38101</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -2945,13 +2927,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>36</xdr:row>
+      <xdr:row>34</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>3905250</xdr:colOff>
-      <xdr:row>60</xdr:row>
+      <xdr:row>58</xdr:row>
       <xdr:rowOff>171449</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -2993,13 +2975,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
+      <xdr:row>87</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>419100</xdr:colOff>
       <xdr:row>89</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>419100</xdr:colOff>
-      <xdr:row>91</xdr:row>
       <xdr:rowOff>9525</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -3041,13 +3023,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>91</xdr:row>
+      <xdr:row>89</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>3905250</xdr:colOff>
-      <xdr:row>116</xdr:row>
+      <xdr:row>114</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -3089,13 +3071,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
+      <xdr:row>114</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>419100</xdr:colOff>
       <xdr:row>116</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>419100</xdr:colOff>
-      <xdr:row>118</xdr:row>
       <xdr:rowOff>38100</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -3137,14 +3119,14 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>118</xdr:row>
+      <xdr:row>116</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>3905250</xdr:colOff>
-      <xdr:row>143</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:row>141</xdr:row>
+      <xdr:rowOff>1</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -3185,14 +3167,14 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
+      <xdr:row>141</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>419100</xdr:colOff>
       <xdr:row>143</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>419100</xdr:colOff>
-      <xdr:row>145</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
+      <xdr:rowOff>38099</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -3233,14 +3215,14 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>145</xdr:row>
+      <xdr:row>143</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>3905250</xdr:colOff>
-      <xdr:row>169</xdr:row>
-      <xdr:rowOff>187022</xdr:rowOff>
+      <xdr:row>167</xdr:row>
+      <xdr:rowOff>187023</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -3281,14 +3263,14 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
+      <xdr:row>168</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>419100</xdr:colOff>
       <xdr:row>170</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>419100</xdr:colOff>
-      <xdr:row>172</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
+      <xdr:rowOff>38101</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -3329,14 +3311,14 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>172</xdr:row>
+      <xdr:row>170</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>3905250</xdr:colOff>
-      <xdr:row>196</xdr:row>
-      <xdr:rowOff>187023</xdr:rowOff>
+      <xdr:row>194</xdr:row>
+      <xdr:rowOff>187022</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -3377,14 +3359,14 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>197</xdr:row>
+      <xdr:row>195</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>228600</xdr:colOff>
-      <xdr:row>198</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
+      <xdr:row>196</xdr:row>
+      <xdr:rowOff>38101</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3439,13 +3421,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>2</xdr:row>
+      <xdr:row>1</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>419100</xdr:colOff>
-      <xdr:row>4</xdr:row>
+      <xdr:row>3</xdr:row>
       <xdr:rowOff>38100</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -3487,13 +3469,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>58</xdr:row>
+      <xdr:row>56</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>3905250</xdr:colOff>
-      <xdr:row>83</xdr:row>
+      <xdr:row>81</xdr:row>
       <xdr:rowOff>1</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -3535,13 +3517,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
+      <xdr:row>59</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>419100</xdr:colOff>
       <xdr:row>61</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>419100</xdr:colOff>
-      <xdr:row>63</xdr:row>
       <xdr:rowOff>38101</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -3583,13 +3565,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>36</xdr:row>
+      <xdr:row>34</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>3905250</xdr:colOff>
-      <xdr:row>60</xdr:row>
+      <xdr:row>58</xdr:row>
       <xdr:rowOff>171449</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -3631,13 +3613,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
+      <xdr:row>87</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>419100</xdr:colOff>
       <xdr:row>89</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>419100</xdr:colOff>
-      <xdr:row>91</xdr:row>
       <xdr:rowOff>9525</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -3679,13 +3661,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>91</xdr:row>
+      <xdr:row>89</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>3905250</xdr:colOff>
-      <xdr:row>116</xdr:row>
+      <xdr:row>114</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -3727,13 +3709,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
+      <xdr:row>114</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>419100</xdr:colOff>
       <xdr:row>116</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>419100</xdr:colOff>
-      <xdr:row>118</xdr:row>
       <xdr:rowOff>38100</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -3775,14 +3757,14 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>118</xdr:row>
+      <xdr:row>116</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>3905250</xdr:colOff>
-      <xdr:row>143</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:row>141</xdr:row>
+      <xdr:rowOff>1</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -3823,14 +3805,14 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
+      <xdr:row>141</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>419100</xdr:colOff>
       <xdr:row>143</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>419100</xdr:colOff>
-      <xdr:row>145</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
+      <xdr:rowOff>38099</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -3871,14 +3853,14 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>145</xdr:row>
+      <xdr:row>143</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>3905250</xdr:colOff>
-      <xdr:row>169</xdr:row>
-      <xdr:rowOff>187022</xdr:rowOff>
+      <xdr:row>167</xdr:row>
+      <xdr:rowOff>187023</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -3919,14 +3901,14 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
+      <xdr:row>168</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>419100</xdr:colOff>
       <xdr:row>170</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>419100</xdr:colOff>
-      <xdr:row>172</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
+      <xdr:rowOff>38101</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -3967,14 +3949,14 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>172</xdr:row>
+      <xdr:row>170</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>3905250</xdr:colOff>
-      <xdr:row>196</xdr:row>
-      <xdr:rowOff>187023</xdr:rowOff>
+      <xdr:row>194</xdr:row>
+      <xdr:rowOff>187022</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -4015,14 +3997,14 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>197</xdr:row>
+      <xdr:row>195</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>228600</xdr:colOff>
-      <xdr:row>198</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
+      <xdr:row>196</xdr:row>
+      <xdr:rowOff>38101</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4077,14 +4059,14 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>79</xdr:row>
+      <xdr:row>77</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>80</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
+      <xdr:row>78</xdr:row>
+      <xdr:rowOff>114301</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -4125,13 +4107,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>57</xdr:row>
+      <xdr:row>55</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>58</xdr:row>
+      <xdr:row>56</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -4173,13 +4155,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>11</xdr:row>
+      <xdr:row>9</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>12</xdr:row>
+      <xdr:row>10</xdr:row>
       <xdr:rowOff>114301</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -4221,13 +4203,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>11</xdr:row>
+      <xdr:row>9</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>12</xdr:row>
+      <xdr:row>10</xdr:row>
       <xdr:rowOff>114301</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -4269,14 +4251,14 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>77</xdr:row>
+      <xdr:row>75</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>78</xdr:row>
-      <xdr:rowOff>114301</xdr:rowOff>
+      <xdr:row>76</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -4601,7 +4583,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D201"/>
+  <dimension ref="A1:D199"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="164" bestFit="1" customWidth="1"/>
@@ -4625,350 +4607,350 @@
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
-        <v>278</v>
-      </c>
-      <c r="B2" s="12" t="s">
-        <v>277</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>276</v>
+      <c r="A2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C2" t="s">
+        <v>208</v>
       </c>
       <c r="D2" t="s">
-        <v>8</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>85</v>
+        <v>186</v>
       </c>
       <c r="B3" t="s">
-        <v>86</v>
+        <v>187</v>
       </c>
       <c r="C3" t="s">
-        <v>222</v>
+        <v>265</v>
       </c>
       <c r="D3" t="s">
-        <v>82</v>
+        <v>42</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>49</v>
+        <v>168</v>
       </c>
       <c r="B4" t="s">
-        <v>50</v>
+        <v>169</v>
       </c>
       <c r="C4" t="s">
-        <v>209</v>
+        <v>256</v>
       </c>
       <c r="D4" t="s">
-        <v>22</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>187</v>
+        <v>57</v>
       </c>
       <c r="B5" t="s">
-        <v>188</v>
+        <v>56</v>
       </c>
       <c r="C5" t="s">
-        <v>267</v>
+        <v>210</v>
       </c>
       <c r="D5" t="s">
-        <v>42</v>
+        <v>58</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>169</v>
+        <v>117</v>
       </c>
       <c r="B6" t="s">
-        <v>170</v>
+        <v>235</v>
       </c>
       <c r="C6" t="s">
-        <v>258</v>
+        <v>234</v>
       </c>
       <c r="D6" t="s">
-        <v>8</v>
+        <v>32</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>57</v>
+        <v>182</v>
       </c>
       <c r="B7" t="s">
-        <v>56</v>
+        <v>183</v>
       </c>
       <c r="C7" t="s">
-        <v>211</v>
+        <v>263</v>
       </c>
       <c r="D7" t="s">
-        <v>58</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>118</v>
+        <v>138</v>
       </c>
       <c r="B8" t="s">
-        <v>237</v>
+        <v>139</v>
       </c>
       <c r="C8" t="s">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="D8" t="s">
-        <v>32</v>
+        <v>122</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>183</v>
+        <v>70</v>
       </c>
       <c r="B9" t="s">
-        <v>184</v>
+        <v>71</v>
       </c>
       <c r="C9" t="s">
-        <v>265</v>
+        <v>215</v>
       </c>
       <c r="D9" t="s">
-        <v>8</v>
+        <v>55</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>139</v>
+        <v>152</v>
       </c>
       <c r="B10" t="s">
-        <v>140</v>
+        <v>151</v>
       </c>
       <c r="C10" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="D10" t="s">
-        <v>123</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="B11" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="C11" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="D11" t="s">
-        <v>55</v>
+        <v>42</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>153</v>
+        <v>18</v>
       </c>
       <c r="B12" t="s">
-        <v>152</v>
-      </c>
-      <c r="C12" t="s">
-        <v>250</v>
+        <v>23</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>196</v>
       </c>
       <c r="D12" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>76</v>
+        <v>28</v>
       </c>
       <c r="B13" t="s">
-        <v>77</v>
+        <v>29</v>
       </c>
       <c r="C13" t="s">
-        <v>219</v>
+        <v>201</v>
       </c>
       <c r="D13" t="s">
-        <v>42</v>
+        <v>19</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>18</v>
+        <v>174</v>
       </c>
       <c r="B14" t="s">
-        <v>23</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>197</v>
+        <v>175</v>
+      </c>
+      <c r="C14" t="s">
+        <v>259</v>
       </c>
       <c r="D14" t="s">
-        <v>19</v>
+        <v>55</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>28</v>
+        <v>118</v>
       </c>
       <c r="B15" t="s">
-        <v>29</v>
+        <v>119</v>
       </c>
       <c r="C15" t="s">
-        <v>202</v>
+        <v>236</v>
       </c>
       <c r="D15" t="s">
-        <v>19</v>
+        <v>82</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>175</v>
+        <v>109</v>
       </c>
       <c r="B16" t="s">
-        <v>176</v>
+        <v>110</v>
       </c>
       <c r="C16" t="s">
-        <v>261</v>
+        <v>272</v>
       </c>
       <c r="D16" t="s">
-        <v>55</v>
+        <v>32</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>119</v>
+        <v>165</v>
       </c>
       <c r="B17" t="s">
-        <v>120</v>
+        <v>166</v>
       </c>
       <c r="C17" t="s">
-        <v>238</v>
+        <v>255</v>
       </c>
       <c r="D17" t="s">
-        <v>82</v>
+        <v>167</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>110</v>
+        <v>184</v>
       </c>
       <c r="B18" t="s">
-        <v>111</v>
+        <v>185</v>
       </c>
       <c r="C18" t="s">
-        <v>274</v>
+        <v>264</v>
       </c>
       <c r="D18" t="s">
-        <v>32</v>
+        <v>42</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>166</v>
+        <v>52</v>
       </c>
       <c r="B19" t="s">
-        <v>167</v>
+        <v>51</v>
       </c>
       <c r="C19" t="s">
-        <v>257</v>
+        <v>209</v>
       </c>
       <c r="D19" t="s">
-        <v>168</v>
+        <v>22</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>185</v>
+        <v>74</v>
       </c>
       <c r="B20" t="s">
-        <v>186</v>
+        <v>75</v>
       </c>
       <c r="C20" t="s">
-        <v>266</v>
+        <v>217</v>
       </c>
       <c r="D20" t="s">
-        <v>42</v>
+        <v>58</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>52</v>
+        <v>159</v>
       </c>
       <c r="B21" t="s">
-        <v>51</v>
+        <v>160</v>
       </c>
       <c r="C21" t="s">
-        <v>210</v>
+        <v>252</v>
       </c>
       <c r="D21" t="s">
-        <v>22</v>
+        <v>122</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>74</v>
+        <v>6</v>
       </c>
       <c r="B22" t="s">
-        <v>75</v>
-      </c>
-      <c r="C22" t="s">
-        <v>218</v>
+        <v>7</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>193</v>
       </c>
       <c r="D22" t="s">
-        <v>58</v>
+        <v>8</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>160</v>
+        <v>59</v>
       </c>
       <c r="B23" t="s">
-        <v>161</v>
+        <v>60</v>
       </c>
       <c r="C23" t="s">
-        <v>254</v>
+        <v>211</v>
       </c>
       <c r="D23" t="s">
-        <v>123</v>
+        <v>58</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>6</v>
+        <v>268</v>
       </c>
       <c r="B24" t="s">
-        <v>7</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>194</v>
+        <v>267</v>
+      </c>
+      <c r="C24" t="s">
+        <v>269</v>
       </c>
       <c r="D24" t="s">
-        <v>8</v>
+        <v>42</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>59</v>
+        <v>86</v>
       </c>
       <c r="B25" t="s">
-        <v>60</v>
+        <v>87</v>
       </c>
       <c r="C25" t="s">
-        <v>212</v>
+        <v>221</v>
       </c>
       <c r="D25" t="s">
-        <v>58</v>
+        <v>82</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>270</v>
+        <v>178</v>
       </c>
       <c r="B26" t="s">
-        <v>269</v>
+        <v>179</v>
       </c>
       <c r="C26" t="s">
-        <v>271</v>
+        <v>261</v>
       </c>
       <c r="D26" t="s">
         <v>42</v>
@@ -4976,86 +4958,83 @@
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>87</v>
+        <v>155</v>
       </c>
       <c r="B27" t="s">
-        <v>88</v>
+        <v>156</v>
       </c>
       <c r="C27" t="s">
-        <v>223</v>
+        <v>250</v>
       </c>
       <c r="D27" t="s">
-        <v>82</v>
+        <v>42</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>179</v>
+        <v>103</v>
       </c>
       <c r="B28" t="s">
-        <v>180</v>
-      </c>
-      <c r="C28" t="s">
-        <v>263</v>
+        <v>104</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>229</v>
       </c>
       <c r="D28" t="s">
-        <v>42</v>
+        <v>82</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>156</v>
+        <v>9</v>
       </c>
       <c r="B29" t="s">
-        <v>157</v>
+        <v>10</v>
       </c>
       <c r="C29" t="s">
-        <v>252</v>
+        <v>194</v>
       </c>
       <c r="D29" t="s">
-        <v>42</v>
+        <v>8</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>104</v>
+        <v>172</v>
       </c>
       <c r="B30" t="s">
-        <v>105</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>231</v>
+        <v>173</v>
+      </c>
+      <c r="C30" t="s">
+        <v>258</v>
       </c>
       <c r="D30" t="s">
-        <v>82</v>
+        <v>55</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>9</v>
+        <v>124</v>
       </c>
       <c r="B31" t="s">
-        <v>10</v>
+        <v>123</v>
       </c>
       <c r="C31" t="s">
-        <v>195</v>
+        <v>238</v>
       </c>
       <c r="D31" t="s">
-        <v>8</v>
+        <v>64</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>173</v>
+        <v>13</v>
       </c>
       <c r="B32" t="s">
-        <v>174</v>
-      </c>
-      <c r="C32" t="s">
-        <v>260</v>
+        <v>14</v>
       </c>
       <c r="D32" t="s">
-        <v>55</v>
+        <v>64</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
@@ -5063,133 +5042,136 @@
         <v>125</v>
       </c>
       <c r="B33" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C33" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="D33" t="s">
-        <v>64</v>
+        <v>127</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>13</v>
+        <v>157</v>
       </c>
       <c r="B34" t="s">
-        <v>14</v>
+        <v>158</v>
+      </c>
+      <c r="C34" t="s">
+        <v>251</v>
       </c>
       <c r="D34" t="s">
-        <v>64</v>
+        <v>42</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>126</v>
+        <v>147</v>
       </c>
       <c r="B35" t="s">
+        <v>148</v>
+      </c>
+      <c r="C35" t="s">
+        <v>247</v>
+      </c>
+      <c r="D35" t="s">
         <v>127</v>
-      </c>
-      <c r="C35" t="s">
-        <v>241</v>
-      </c>
-      <c r="D35" t="s">
-        <v>128</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>158</v>
+        <v>39</v>
       </c>
       <c r="B36" t="s">
-        <v>159</v>
+        <v>38</v>
       </c>
       <c r="C36" t="s">
-        <v>253</v>
+        <v>204</v>
       </c>
       <c r="D36" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A37" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="B37" t="s">
+        <v>92</v>
+      </c>
+      <c r="C37" t="s">
+        <v>224</v>
+      </c>
+      <c r="D37" t="s">
         <v>42</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
-        <v>148</v>
-      </c>
-      <c r="B37" t="s">
-        <v>149</v>
-      </c>
-      <c r="C37" t="s">
-        <v>249</v>
-      </c>
-      <c r="D37" t="s">
-        <v>128</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>39</v>
-      </c>
-      <c r="B38" t="s">
-        <v>38</v>
+        <v>37</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>36</v>
       </c>
       <c r="C38" t="s">
-        <v>205</v>
+        <v>198</v>
       </c>
       <c r="D38" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A39" s="3" t="s">
-        <v>94</v>
+      <c r="A39" t="s">
+        <v>113</v>
       </c>
       <c r="B39" t="s">
-        <v>93</v>
+        <v>114</v>
       </c>
       <c r="C39" t="s">
-        <v>226</v>
+        <v>233</v>
       </c>
       <c r="D39" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>37</v>
-      </c>
-      <c r="B40" s="2" t="s">
-        <v>36</v>
+        <v>188</v>
+      </c>
+      <c r="B40" t="s">
+        <v>189</v>
       </c>
       <c r="C40" t="s">
-        <v>199</v>
+        <v>266</v>
       </c>
       <c r="D40" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>114</v>
+        <v>94</v>
       </c>
       <c r="B41" t="s">
-        <v>115</v>
+        <v>95</v>
       </c>
       <c r="C41" t="s">
-        <v>235</v>
+        <v>225</v>
       </c>
       <c r="D41" t="s">
-        <v>32</v>
+        <v>96</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>189</v>
+        <v>111</v>
       </c>
       <c r="B42" t="s">
-        <v>190</v>
+        <v>112</v>
       </c>
       <c r="C42" t="s">
-        <v>268</v>
+        <v>232</v>
       </c>
       <c r="D42" t="s">
         <v>32</v>
@@ -5197,626 +5179,604 @@
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>95</v>
+        <v>62</v>
       </c>
       <c r="B43" t="s">
-        <v>96</v>
+        <v>61</v>
       </c>
       <c r="C43" t="s">
-        <v>227</v>
+        <v>271</v>
       </c>
       <c r="D43" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>112</v>
+        <v>72</v>
       </c>
       <c r="B44" t="s">
-        <v>113</v>
+        <v>73</v>
       </c>
       <c r="C44" t="s">
-        <v>234</v>
+        <v>216</v>
       </c>
       <c r="D44" t="s">
-        <v>32</v>
+        <v>45</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>62</v>
+        <v>132</v>
       </c>
       <c r="B45" t="s">
-        <v>61</v>
+        <v>133</v>
       </c>
       <c r="C45" t="s">
         <v>273</v>
       </c>
       <c r="D45" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>72</v>
+        <v>115</v>
       </c>
       <c r="B46" t="s">
-        <v>73</v>
+        <v>116</v>
       </c>
       <c r="C46" t="s">
-        <v>217</v>
+        <v>199</v>
       </c>
       <c r="D46" t="s">
-        <v>45</v>
+        <v>24</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>133</v>
+        <v>97</v>
       </c>
       <c r="B47" t="s">
-        <v>134</v>
+        <v>98</v>
       </c>
       <c r="C47" t="s">
-        <v>275</v>
+        <v>226</v>
       </c>
       <c r="D47" t="s">
-        <v>58</v>
+        <v>96</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>116</v>
+        <v>53</v>
       </c>
       <c r="B48" t="s">
-        <v>117</v>
+        <v>54</v>
       </c>
       <c r="C48" t="s">
-        <v>200</v>
+        <v>270</v>
       </c>
       <c r="D48" t="s">
-        <v>24</v>
+        <v>55</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>98</v>
-      </c>
-      <c r="B49" t="s">
-        <v>99</v>
-      </c>
-      <c r="C49" t="s">
-        <v>228</v>
+        <v>5</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>192</v>
       </c>
       <c r="D49" t="s">
-        <v>97</v>
+        <v>8</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A50" t="s">
-        <v>53</v>
+      <c r="A50" s="3" t="s">
+        <v>91</v>
       </c>
       <c r="B50" t="s">
-        <v>54</v>
+        <v>90</v>
       </c>
       <c r="C50" t="s">
-        <v>272</v>
+        <v>223</v>
       </c>
       <c r="D50" t="s">
-        <v>55</v>
+        <v>8</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>5</v>
-      </c>
-      <c r="B51" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C51" s="2" t="s">
-        <v>193</v>
+        <v>180</v>
+      </c>
+      <c r="B51" t="s">
+        <v>181</v>
+      </c>
+      <c r="C51" t="s">
+        <v>262</v>
       </c>
       <c r="D51" t="s">
-        <v>8</v>
+        <v>42</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A52" s="3" t="s">
-        <v>92</v>
+      <c r="A52" t="s">
+        <v>43</v>
       </c>
       <c r="B52" t="s">
-        <v>91</v>
+        <v>44</v>
       </c>
       <c r="C52" t="s">
-        <v>225</v>
+        <v>206</v>
       </c>
       <c r="D52" t="s">
-        <v>8</v>
+        <v>45</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>181</v>
-      </c>
-      <c r="B53" t="s">
-        <v>182</v>
+        <v>30</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>31</v>
       </c>
       <c r="C53" t="s">
-        <v>264</v>
+        <v>202</v>
       </c>
       <c r="D53" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>43</v>
+        <v>154</v>
       </c>
       <c r="B54" t="s">
-        <v>44</v>
+        <v>153</v>
       </c>
       <c r="C54" t="s">
-        <v>207</v>
+        <v>249</v>
       </c>
       <c r="D54" t="s">
-        <v>45</v>
+        <v>8</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>30</v>
-      </c>
-      <c r="B55" s="2" t="s">
-        <v>31</v>
+        <v>150</v>
+      </c>
+      <c r="B55" t="s">
+        <v>149</v>
       </c>
       <c r="C55" t="s">
-        <v>203</v>
+        <v>190</v>
       </c>
       <c r="D55" t="s">
-        <v>32</v>
+        <v>42</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>155</v>
+        <v>140</v>
       </c>
       <c r="B56" t="s">
-        <v>154</v>
+        <v>141</v>
       </c>
       <c r="C56" t="s">
-        <v>251</v>
+        <v>244</v>
       </c>
       <c r="D56" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A57" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="B57" t="s">
+        <v>88</v>
+      </c>
+      <c r="C57" t="s">
+        <v>222</v>
+      </c>
+      <c r="D57" t="s">
         <v>8</v>
-      </c>
-    </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A57" t="s">
-        <v>151</v>
-      </c>
-      <c r="B57" t="s">
-        <v>150</v>
-      </c>
-      <c r="C57" t="s">
-        <v>191</v>
-      </c>
-      <c r="D57" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>141</v>
+        <v>99</v>
       </c>
       <c r="B58" t="s">
-        <v>142</v>
+        <v>100</v>
       </c>
       <c r="C58" t="s">
-        <v>246</v>
+        <v>227</v>
       </c>
       <c r="D58" t="s">
-        <v>143</v>
+        <v>96</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A59" s="3" t="s">
-        <v>90</v>
+      <c r="A59" t="s">
+        <v>15</v>
       </c>
       <c r="B59" t="s">
-        <v>89</v>
+        <v>16</v>
       </c>
       <c r="C59" t="s">
-        <v>224</v>
+        <v>195</v>
       </c>
       <c r="D59" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>100</v>
+        <v>143</v>
       </c>
       <c r="B60" t="s">
-        <v>101</v>
+        <v>144</v>
       </c>
       <c r="C60" t="s">
-        <v>229</v>
+        <v>245</v>
       </c>
       <c r="D60" t="s">
-        <v>97</v>
+        <v>142</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>15</v>
+        <v>145</v>
       </c>
       <c r="B61" t="s">
-        <v>16</v>
+        <v>146</v>
       </c>
       <c r="C61" t="s">
-        <v>196</v>
+        <v>246</v>
       </c>
       <c r="D61" t="s">
-        <v>17</v>
+        <v>142</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>144</v>
+        <v>63</v>
       </c>
       <c r="B62" t="s">
-        <v>145</v>
+        <v>69</v>
       </c>
       <c r="C62" t="s">
-        <v>247</v>
+        <v>212</v>
       </c>
       <c r="D62" t="s">
-        <v>143</v>
+        <v>42</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>146</v>
+        <v>46</v>
       </c>
       <c r="B63" t="s">
-        <v>147</v>
+        <v>47</v>
       </c>
       <c r="C63" t="s">
-        <v>248</v>
+        <v>207</v>
       </c>
       <c r="D63" t="s">
-        <v>143</v>
+        <v>48</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>63</v>
+        <v>130</v>
       </c>
       <c r="B64" t="s">
-        <v>69</v>
+        <v>131</v>
       </c>
       <c r="C64" t="s">
-        <v>213</v>
+        <v>241</v>
       </c>
       <c r="D64" t="s">
-        <v>42</v>
+        <v>58</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="B65" t="s">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="C65" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="D65" t="s">
-        <v>48</v>
+        <v>35</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>131</v>
+        <v>170</v>
       </c>
       <c r="B66" t="s">
-        <v>132</v>
+        <v>171</v>
       </c>
       <c r="C66" t="s">
-        <v>243</v>
+        <v>257</v>
       </c>
       <c r="D66" t="s">
-        <v>58</v>
+        <v>42</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>33</v>
+        <v>67</v>
       </c>
       <c r="B67" t="s">
-        <v>34</v>
+        <v>68</v>
       </c>
       <c r="C67" t="s">
-        <v>204</v>
+        <v>214</v>
       </c>
       <c r="D67" t="s">
-        <v>35</v>
+        <v>8</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>171</v>
+        <v>66</v>
       </c>
       <c r="B68" t="s">
-        <v>172</v>
+        <v>65</v>
       </c>
       <c r="C68" t="s">
-        <v>259</v>
+        <v>213</v>
       </c>
       <c r="D68" t="s">
-        <v>42</v>
+        <v>8</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>67</v>
+        <v>134</v>
       </c>
       <c r="B69" t="s">
-        <v>68</v>
+        <v>135</v>
       </c>
       <c r="C69" t="s">
-        <v>215</v>
+        <v>242</v>
       </c>
       <c r="D69" t="s">
-        <v>8</v>
+        <v>55</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>66</v>
+        <v>105</v>
       </c>
       <c r="B70" t="s">
-        <v>65</v>
+        <v>106</v>
       </c>
       <c r="C70" t="s">
-        <v>214</v>
+        <v>230</v>
       </c>
       <c r="D70" t="s">
-        <v>8</v>
+        <v>32</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>135</v>
+        <v>107</v>
       </c>
       <c r="B71" t="s">
-        <v>136</v>
-      </c>
-      <c r="C71" t="s">
-        <v>244</v>
+        <v>108</v>
+      </c>
+      <c r="C71" s="2" t="s">
+        <v>231</v>
       </c>
       <c r="D71" t="s">
-        <v>55</v>
+        <v>32</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>106</v>
+        <v>78</v>
       </c>
       <c r="B72" t="s">
-        <v>107</v>
+        <v>79</v>
       </c>
       <c r="C72" t="s">
-        <v>232</v>
+        <v>219</v>
       </c>
       <c r="D72" t="s">
-        <v>32</v>
+        <v>42</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="B73" t="s">
-        <v>109</v>
-      </c>
-      <c r="C73" s="2" t="s">
-        <v>233</v>
+        <v>102</v>
+      </c>
+      <c r="C73" t="s">
+        <v>228</v>
       </c>
       <c r="D73" t="s">
-        <v>32</v>
+        <v>42</v>
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>78</v>
+        <v>129</v>
       </c>
       <c r="B74" t="s">
-        <v>79</v>
+        <v>128</v>
       </c>
       <c r="C74" t="s">
-        <v>220</v>
+        <v>240</v>
       </c>
       <c r="D74" t="s">
-        <v>42</v>
+        <v>122</v>
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>102</v>
+        <v>120</v>
       </c>
       <c r="B75" t="s">
-        <v>103</v>
+        <v>121</v>
       </c>
       <c r="C75" t="s">
-        <v>230</v>
+        <v>237</v>
       </c>
       <c r="D75" t="s">
-        <v>42</v>
+        <v>122</v>
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>130</v>
+        <v>161</v>
       </c>
       <c r="B76" t="s">
-        <v>129</v>
+        <v>162</v>
       </c>
       <c r="C76" t="s">
-        <v>242</v>
+        <v>253</v>
       </c>
       <c r="D76" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>121</v>
+        <v>81</v>
       </c>
       <c r="B77" t="s">
-        <v>122</v>
+        <v>80</v>
       </c>
       <c r="C77" t="s">
-        <v>239</v>
+        <v>220</v>
       </c>
       <c r="D77" t="s">
-        <v>123</v>
+        <v>82</v>
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>162</v>
+        <v>137</v>
       </c>
       <c r="B78" t="s">
-        <v>163</v>
-      </c>
-      <c r="C78" t="s">
-        <v>255</v>
+        <v>136</v>
       </c>
       <c r="D78" t="s">
-        <v>123</v>
+        <v>8</v>
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>81</v>
+        <v>163</v>
       </c>
       <c r="B79" t="s">
-        <v>80</v>
+        <v>164</v>
       </c>
       <c r="C79" t="s">
-        <v>221</v>
+        <v>254</v>
       </c>
       <c r="D79" t="s">
-        <v>82</v>
+        <v>127</v>
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>138</v>
+        <v>40</v>
       </c>
       <c r="B80" t="s">
-        <v>137</v>
+        <v>41</v>
+      </c>
+      <c r="C80" t="s">
+        <v>205</v>
       </c>
       <c r="D80" t="s">
-        <v>8</v>
+        <v>42</v>
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>164</v>
+        <v>176</v>
       </c>
       <c r="B81" t="s">
-        <v>165</v>
+        <v>177</v>
       </c>
       <c r="C81" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>128</v>
+        <v>42</v>
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>40</v>
-      </c>
-      <c r="B82" t="s">
-        <v>41</v>
-      </c>
-      <c r="C82" t="s">
-        <v>206</v>
+        <v>11</v>
+      </c>
+      <c r="B82" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C82" s="2" t="s">
+        <v>191</v>
       </c>
       <c r="D82" t="s">
-        <v>42</v>
+        <v>27</v>
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>177</v>
+        <v>25</v>
       </c>
       <c r="B83" t="s">
-        <v>178</v>
+        <v>26</v>
       </c>
       <c r="C83" t="s">
-        <v>262</v>
+        <v>200</v>
       </c>
       <c r="D83" t="s">
-        <v>42</v>
+        <v>27</v>
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C84" s="2" t="s">
-        <v>192</v>
+        <v>21</v>
+      </c>
+      <c r="C84" t="s">
+        <v>197</v>
       </c>
       <c r="D84" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A85" t="s">
-        <v>25</v>
-      </c>
-      <c r="B85" t="s">
-        <v>26</v>
-      </c>
-      <c r="C85" t="s">
-        <v>201</v>
-      </c>
-      <c r="D85" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A86" t="s">
-        <v>20</v>
-      </c>
-      <c r="B86" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C86" t="s">
-        <v>198</v>
-      </c>
-      <c r="D86" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="89" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="90" spans="1:4" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A90" s="10"/>
-    </row>
-    <row r="91" spans="1:4" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="88" spans="1:4" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A88" s="10"/>
+    </row>
+    <row r="89" spans="1:4" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A89" s="4"/>
+    </row>
+    <row r="90" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A90" s="5"/>
+    </row>
+    <row r="91" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A91" s="4"/>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A92" s="5"/>
+      <c r="A92" s="4"/>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A93" s="4"/>
@@ -5882,22 +5842,22 @@
       <c r="A113" s="4"/>
     </row>
     <row r="114" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A114" s="4"/>
+      <c r="A114" s="6"/>
     </row>
     <row r="115" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A115" s="4"/>
+      <c r="A115" s="6"/>
     </row>
     <row r="116" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A116" s="6"/>
+      <c r="A116" s="4"/>
     </row>
     <row r="117" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A117" s="6"/>
+      <c r="A117" s="5"/>
     </row>
     <row r="118" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A118" s="4"/>
     </row>
     <row r="119" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A119" s="5"/>
+      <c r="A119" s="4"/>
     </row>
     <row r="120" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A120" s="4"/>
@@ -5963,22 +5923,22 @@
       <c r="A140" s="4"/>
     </row>
     <row r="141" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A141" s="4"/>
+      <c r="A141" s="6"/>
     </row>
     <row r="142" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A142" s="4"/>
+      <c r="A142" s="6"/>
     </row>
     <row r="143" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A143" s="6"/>
+      <c r="A143" s="4"/>
     </row>
     <row r="144" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A144" s="6"/>
+      <c r="A144" s="5"/>
     </row>
     <row r="145" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A145" s="4"/>
     </row>
     <row r="146" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A146" s="5"/>
+      <c r="A146" s="4"/>
     </row>
     <row r="147" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A147" s="4"/>
@@ -6044,22 +6004,22 @@
       <c r="A167" s="4"/>
     </row>
     <row r="168" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A168" s="4"/>
+      <c r="A168" s="6"/>
     </row>
     <row r="169" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A169" s="4"/>
+      <c r="A169" s="6"/>
     </row>
     <row r="170" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A170" s="6"/>
+      <c r="A170" s="4"/>
     </row>
     <row r="171" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A171" s="6"/>
+      <c r="A171" s="5"/>
     </row>
     <row r="172" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A172" s="4"/>
     </row>
     <row r="173" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A173" s="5"/>
+      <c r="A173" s="4"/>
     </row>
     <row r="174" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A174" s="4"/>
@@ -6125,29 +6085,23 @@
       <c r="A194" s="4"/>
     </row>
     <row r="195" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A195" s="4"/>
+      <c r="A195" s="7"/>
     </row>
     <row r="196" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A196" s="4"/>
+      <c r="A196" s="7"/>
     </row>
     <row r="197" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A197" s="7"/>
+      <c r="A197" s="8" t="s">
+        <v>83</v>
+      </c>
     </row>
     <row r="198" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A198" s="7"/>
-    </row>
-    <row r="199" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A199" s="8" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="200" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A200" s="9" t="s">
+      <c r="A198" s="9" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="201" spans="1:1" ht="21.75" x14ac:dyDescent="0.25">
-      <c r="A201" s="11" t="s">
+    <row r="199" spans="1:1" ht="21.75" x14ac:dyDescent="0.25">
+      <c r="A199" s="11" t="s">
         <v>85</v>
       </c>
     </row>
@@ -6158,20 +6112,18 @@
     </sortState>
   </autoFilter>
   <hyperlinks>
-    <hyperlink ref="B51" r:id="rId1" xr:uid="{DCE316A2-6F5F-4239-8670-A2501AD068BA}"/>
-    <hyperlink ref="B84" r:id="rId2" xr:uid="{E75C36C1-9EBF-4C4A-9D5E-6178C36287DA}"/>
-    <hyperlink ref="B86" r:id="rId3" xr:uid="{E7AF4AD0-FB67-4D18-A345-7AC735B2DDD9}"/>
-    <hyperlink ref="B40" r:id="rId4" xr:uid="{5ED3D7ED-FC6D-4C44-8B5F-671739F6A728}"/>
-    <hyperlink ref="B55" r:id="rId5" xr:uid="{AED35A75-AE1C-4AD0-9122-E943C0451F4B}"/>
-    <hyperlink ref="A199" r:id="rId6" location="redirect=landing_international&amp;origin=vip" display="https://www.mercadolivre.com.br/importados/compra-internacional - redirect=landing_international&amp;origin=vip" xr:uid="{CC0DCAE0-A290-49ED-AC96-9E0C27938302}"/>
-    <hyperlink ref="B16" r:id="rId7" xr:uid="{C44C884A-2B1F-46D5-849E-2AEEA7727C26}"/>
-    <hyperlink ref="C73" r:id="rId8" xr:uid="{D7CE1F55-B7E3-4E3A-87FB-E2DE297FF331}"/>
-    <hyperlink ref="C84" r:id="rId9" xr:uid="{7F6784A7-D9C7-49C7-ADDF-58FC99A98E87}"/>
-    <hyperlink ref="A2" r:id="rId10" display="https://lista.mercadolivre.com.br/loja/arno/" xr:uid="{C2FE83C8-65E9-44C2-AED5-3D82B99C1460}"/>
-    <hyperlink ref="C2" r:id="rId11" xr:uid="{A62E20C5-F356-49A0-8D26-E46AD707FE03}"/>
+    <hyperlink ref="B49" r:id="rId1" xr:uid="{DCE316A2-6F5F-4239-8670-A2501AD068BA}"/>
+    <hyperlink ref="B82" r:id="rId2" xr:uid="{E75C36C1-9EBF-4C4A-9D5E-6178C36287DA}"/>
+    <hyperlink ref="B84" r:id="rId3" xr:uid="{E7AF4AD0-FB67-4D18-A345-7AC735B2DDD9}"/>
+    <hyperlink ref="B38" r:id="rId4" xr:uid="{5ED3D7ED-FC6D-4C44-8B5F-671739F6A728}"/>
+    <hyperlink ref="B53" r:id="rId5" xr:uid="{AED35A75-AE1C-4AD0-9122-E943C0451F4B}"/>
+    <hyperlink ref="A197" r:id="rId6" location="redirect=landing_international&amp;origin=vip" display="https://www.mercadolivre.com.br/importados/compra-internacional - redirect=landing_international&amp;origin=vip" xr:uid="{CC0DCAE0-A290-49ED-AC96-9E0C27938302}"/>
+    <hyperlink ref="B14" r:id="rId7" xr:uid="{C44C884A-2B1F-46D5-849E-2AEEA7727C26}"/>
+    <hyperlink ref="C71" r:id="rId8" xr:uid="{D7CE1F55-B7E3-4E3A-87FB-E2DE297FF331}"/>
+    <hyperlink ref="C82" r:id="rId9" xr:uid="{7F6784A7-D9C7-49C7-ADDF-58FC99A98E87}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId12"/>
-  <drawing r:id="rId13"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId10"/>
+  <drawing r:id="rId11"/>
 </worksheet>
 </file>